--- a/03_Outputs/Penderisco_Sinifana/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Penderisco_Sinifana/03_Ordenamiento/ordenamiento.xlsx
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="E7" s="112">
-        <v>0.164148337101217</v>
+        <v>0.164148337101218</v>
       </c>
     </row>
     <row r="8">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.164148337101217</v>
+        <v>0.164148337101218</v>
       </c>
     </row>
     <row r="8">
